--- a/UPDATE_NEXT_OFFERS/Release note  UPDATE_MOBANK_NEXT_OFFERS UAT.xlsx
+++ b/UPDATE_NEXT_OFFERS/Release note  UPDATE_MOBANK_NEXT_OFFERS UAT.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7095"/>
+    <workbookView windowWidth="19815" windowHeight="7815"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -171,10 +171,10 @@
     <t>Implementation Plan</t>
   </si>
   <si>
-    <t>Release notes UAT
+    <t>Release notes PROD
 Implementation Steps:
 App Deployment Team,
-Servers: 10.80.93.141/142
+Servers: 10.80.65.211/212/213/214
 1. Please get the source code from "deliverables"  in below mentioned svn.
 http://munmvs0905.ratnakarbank.in/svn/Enterprise_Services_Development/branches/NodeJsProjects/MOBANK_NEXT_OFFERS/UPDATE_MOBANK_NEXT_OFFERS
 Place the source code in /app
@@ -182,18 +182,16 @@
 http://munmvs0905.ratnakarbank.in/svn/Enterprise_Services_Development/branches/NodeJsProjects/DEPENDENCIES
 Place the NodeLibs.zip in /app and unzip the same.
 3. Do following environment and config changes
- set uat as running environment
+ set prod as running environment
  -Goto directory '/app/MOBANK_NEXT_OFFERS/UPDATE_MOBANK_NEXT_OFFERS/config' and open file 'config.js'
  -Find the line "process.env.NODE_ENV = 'dev'
-  Replace 'dev' with 'uat'
-4. Execute the following command
-npm config set store-dir /app/NodeLibs/
+  Replace 'dev' with 'prod'
+4. Copy DB Password from /app/PREAPPROVED_AND_SECURE_CREDIT_CARDS/GET_SCHEME_LISTS/config/.prod.env =&gt; .prod.env file.
+5. Execute the following command
 cd /app/
 cd MOBANK_NEXT_OFFERS/UPDATE_MOBANK_NEXT_OFFERS/
-pnpm i -r --offline
-5. Execute below commands
- cd MOBANK_NEXT_OFFERS/UPDATE_MOBANK_NEXT_OFFERS/
- pm2 start ecosystem.config.js
+pnpm i --offline
+sh run.sh &amp;
 6. Nginx Configuration 
    Please get the config files in below mentioned svn path.
    http://munmvs0905.ratnakarbank.in/svn/Enterprise_Services_Development/branches/NodeJsProjects/MOBANK_NEXT_OFFERS/UPDATE_MOBANK_NEXT_OFFERS/prop
@@ -211,7 +209,7 @@
   <si>
     <t xml:space="preserve">Follow Below steps to stop server and restart the configruation 
 Step 1: cd /app/MOBANK_NEXT_OFFERS/UPDATE_MOBANK_NEXT_OFFERS
-Step 2:  pm2 stop ecosystem.config.js
+Step 2:  sh kill.sh &amp;
 Step 3: netstat -nlp | grep 4063
              - If this command give below message then target server is stop.
              - Not all processes could be identified, non-owned process info
@@ -249,25 +247,25 @@
     <t>UAT</t>
   </si>
   <si>
-    <t>Servers: 10.80.93.141/142
+    <t>UAT Sign. Off</t>
+  </si>
+  <si>
+    <t>UAT Sign-Off By</t>
+  </si>
+  <si>
+    <t>UAT Release ID</t>
+  </si>
+  <si>
+    <t>Change Request No</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>Servers:10.80.65.211/212/213/214
 User : appuser
 Port: 22
 files: MOBANK_NEXT_OFFERS/UPDATE_MOBANK_NEXT_OFFERS.zip, Nginx.conf</t>
-  </si>
-  <si>
-    <t>UAT Sign. Off</t>
-  </si>
-  <si>
-    <t>UAT Sign-Off By</t>
-  </si>
-  <si>
-    <t>UAT Release ID</t>
-  </si>
-  <si>
-    <t>Change Request No</t>
-  </si>
-  <si>
-    <t>Production</t>
   </si>
   <si>
     <t>Change Status</t>
@@ -282,10 +280,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="25">
     <font>
@@ -318,6 +316,82 @@
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -328,51 +402,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -381,36 +410,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
@@ -418,14 +417,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
@@ -434,7 +425,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -448,6 +439,20 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,13 +461,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -502,13 +500,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -520,43 +662,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -566,128 +684,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -722,15 +720,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thick">
         <color auto="1"/>
       </left>
@@ -738,30 +727,6 @@
       <top/>
       <bottom style="thick">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -805,6 +770,30 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -822,6 +811,15 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -830,19 +828,10 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -850,132 +839,132 @@
     <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="17" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1034,11 +1023,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="17" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="17" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="17" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="17" applyBorder="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="17" applyBorder="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="17" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1379,7 +1364,7 @@
     <col min="257" max="1025" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" ht="15.75" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1408,7 +1393,7 @@
       <c r="J1" s="16"/>
       <c r="K1" s="16"/>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" ht="15.75" spans="1:11">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
@@ -1421,7 +1406,7 @@
       <c r="J2" s="16"/>
       <c r="K2" s="16"/>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" ht="15.75" spans="1:11">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
@@ -1695,9 +1680,7 @@
       <c r="A21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>26</v>
-      </c>
+      <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16"/>
@@ -1734,7 +1717,7 @@
       <c r="J23" s="17"/>
       <c r="K23" s="25"/>
     </row>
-    <row r="24" ht="68.3" customHeight="1" spans="1:11">
+    <row r="24" ht="9" customHeight="1" spans="1:11">
       <c r="A24" s="2"/>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -1749,26 +1732,26 @@
     </row>
     <row r="25" ht="18.85" customHeight="1" spans="1:11">
       <c r="A25" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B25" s="21"/>
       <c r="C25" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D25" s="16"/>
       <c r="E25" s="16"/>
       <c r="F25" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G25" s="22"/>
       <c r="H25" s="23"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
       <c r="K25" s="25"/>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:11">
       <c r="A26" s="24" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="16"/>
@@ -1777,14 +1760,18 @@
       <c r="F26" s="16"/>
       <c r="G26" s="16"/>
       <c r="H26" s="16"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
       <c r="K26" s="25"/>
     </row>
     <row r="27" ht="15.75" spans="1:11">
       <c r="A27" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="19" t="s">
         <v>31</v>
       </c>
+      <c r="C27" s="19"/>
       <c r="D27" s="26"/>
       <c r="G27" s="17"/>
       <c r="H27" s="17"/>
@@ -1794,8 +1781,8 @@
     </row>
     <row r="28" ht="15.75" spans="1:11">
       <c r="A28" s="2"/>
-      <c r="B28" s="27"/>
-      <c r="C28" s="28"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
@@ -1804,16 +1791,19 @@
     </row>
     <row r="29" ht="15.75" spans="1:11">
       <c r="A29" s="2"/>
-      <c r="C29" s="28"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
       <c r="G29" s="17"/>
       <c r="H29" s="17"/>
       <c r="I29" s="17"/>
       <c r="J29" s="17"/>
       <c r="K29" s="25"/>
     </row>
-    <row r="30" ht="15.75" spans="1:11">
+    <row r="30" ht="61" customHeight="1" spans="1:11">
       <c r="A30" s="2"/>
-      <c r="D30" s="29"/>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="27"/>
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
       <c r="I30" s="17"/>
@@ -1825,11 +1815,11 @@
         <v>32</v>
       </c>
       <c r="B31" s="17"/>
-      <c r="C31" s="30"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="32" t="s">
+      <c r="C31" s="28"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30" t="s">
         <v>33</v>
       </c>
       <c r="H31" s="17"/>
@@ -1840,11 +1830,11 @@
     <row r="32" ht="18" customHeight="1" spans="1:11">
       <c r="A32" s="2"/>
       <c r="B32" s="17"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="32"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="30"/>
       <c r="H32" s="17"/>
       <c r="I32" s="17"/>
       <c r="J32" s="25"/>
@@ -1854,10 +1844,10 @@
       <c r="A33" s="2"/>
       <c r="B33" s="17"/>
       <c r="C33" s="25"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="32"/>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="30"/>
       <c r="H33" s="17"/>
       <c r="I33" s="17"/>
       <c r="J33" s="25"/>
@@ -1868,7 +1858,7 @@
     <row r="38" ht="52.2" customHeight="1"/>
     <row r="43" ht="24.25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="50">
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G15:H15"/>
@@ -1918,6 +1908,7 @@
     <mergeCell ref="G27:H30"/>
     <mergeCell ref="I27:J30"/>
     <mergeCell ref="H31:I33"/>
+    <mergeCell ref="B27:C30"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="C1 B5:E5 C6:E14"/>
